--- a/results/ncbc_s10/TM_p6/reference_peaks.xlsx
+++ b/results/ncbc_s10/TM_p6/reference_peaks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C325"/>
+  <dimension ref="A1:C296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7453122895540619</v>
+        <v>0.8061744575505787</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6585166711540552</v>
+        <v>0.8305466195374498</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9221802602181955</v>
+        <v>0.9335425023498419</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8929325389962643</v>
+        <v>0.9797979797979802</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8906781422994117</v>
+        <v>1.091279770178852</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9628798552932916</v>
+        <v>1.019288560572963</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9818549497270316</v>
+        <v>1.018931119848551</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9402878549502902</v>
+        <v>1.007334154123145</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9484173273905653</v>
+        <v>1.069833326714061</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8899558574359675</v>
+        <v>1.095264572328789</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.018520635123513</v>
+        <v>1.038378542965699</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.041021221536866</v>
+        <v>0.9981333651058422</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9107580697851789</v>
+        <v>1.052133391582933</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9742422901388336</v>
+        <v>1.108357493678595</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9462168774538399</v>
+        <v>1.045725935634192</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9533758292557474</v>
+        <v>1.142446747951335</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9742948510753632</v>
+        <v>0.9862319128374174</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9910126973816783</v>
+        <v>1.027496458689119</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9826016334476302</v>
+        <v>1.045540595999312</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9580835697581322</v>
+        <v>1.017024769318347</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.030076244658378</v>
+        <v>1.046837973443478</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.020146759449051</v>
+        <v>1.061850483868833</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9877869757714657</v>
+        <v>1.069489124535001</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9499420255245772</v>
+        <v>1.076267259753498</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.042679634921763</v>
+        <v>1.065213074387386</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9446088635340416</v>
+        <v>1.044587420734213</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.027545178552553</v>
+        <v>1.062684512225797</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9626263241281856</v>
+        <v>1.09946119120431</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.8720455340093737</v>
+        <v>1.050121132689935</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9933834792937066</v>
+        <v>1.016323126414874</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9375471793243892</v>
+        <v>1.024875226710089</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.04556650790678</v>
+        <v>1.05021380250738</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9240136817791234</v>
+        <v>1.035704356805271</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.012062691127687</v>
+        <v>1.009055165018464</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9757829508350065</v>
+        <v>1.04155579384937</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.006582284442401</v>
+        <v>1.030594278300702</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.927198242110164</v>
+        <v>1.051643565405033</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9936727015820838</v>
+        <v>1.086619802216138</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9831635027773313</v>
+        <v>1.100003971563605</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9548239951424875</v>
+        <v>1.011994122085865</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9819879900214954</v>
+        <v>1.002912479976695</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9990046291016199</v>
+        <v>1.031573930656499</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9551612268631641</v>
+        <v>1.038140249149423</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9623403406591295</v>
+        <v>1.112911553278526</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.001809344738056</v>
+        <v>0.9859803804757933</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.002147006402149</v>
+        <v>1.032963977918107</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9681812178696245</v>
+        <v>1.056833075181699</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9909299399637844</v>
+        <v>1.054887009015449</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9767670309586258</v>
+        <v>1.09412605742881</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9605447859616555</v>
+        <v>1.08508413095568</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.9272323374548141</v>
+        <v>1.024411877622887</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.007599072045517</v>
+        <v>1.028251055773992</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9719635964424232</v>
+        <v>0.9680024358923495</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9934243993104863</v>
+        <v>1.039265525504057</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.006908979168951</v>
+        <v>1.03594265062155</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.8571915983870266</v>
+        <v>1.026993393965869</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.00225982440113</v>
+        <v>1.08664627930683</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.058228935236559</v>
+        <v>1.052027483220144</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.024886114301022</v>
+        <v>1.055469505010789</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.8998455917963095</v>
+        <v>1.023233647086858</v>
       </c>
     </row>
     <row r="62">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.9573144725564031</v>
+        <v>1.022465811456637</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.025049223949688</v>
+        <v>1.106782106782107</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.9612209797923147</v>
+        <v>1.07692918702093</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.909416330562292</v>
+        <v>0.9932351033268464</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.996225871085556</v>
+        <v>1.083654368058038</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.9531499041311088</v>
+        <v>1.014787455154428</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.9328892898391133</v>
+        <v>1.07334154123145</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.9303781961007699</v>
+        <v>1.023418986721739</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.8893293827990713</v>
+        <v>1.027509697234468</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.9344883719431659</v>
+        <v>1.100374650833366</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.9137876149441309</v>
+        <v>1.022584958364776</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.9922909663191012</v>
+        <v>1.031732793200683</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.9722174204865675</v>
+        <v>1.047036551623702</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.040309924893324</v>
+        <v>1.032196142287885</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.9042347346137443</v>
+        <v>1.0563697260945</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.00957370057249</v>
+        <v>1.076730608840701</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.9305453204318986</v>
+        <v>0.9954724174907662</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.9541072265266449</v>
+        <v>0.9717754213167057</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.022333975018365</v>
+        <v>1.058487893350279</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.9044115094753341</v>
+        <v>1.05779948899215</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.9731857053455366</v>
+        <v>1.05789215880959</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.012399106979039</v>
+        <v>1.061956392231622</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.9002878829264598</v>
+        <v>1.028740881951888</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.9432571854126609</v>
+        <v>1.025139997617062</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.9836678820210379</v>
+        <v>1.057759773356104</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.009579851363756</v>
+        <v>1.063968651124614</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.022153160032276</v>
+        <v>1.096230986139247</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.9199263979231932</v>
+        <v>1.050438857778302</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.9843144085951022</v>
+        <v>1.126745833167851</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.971474080191955</v>
+        <v>1.074956643763981</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.009325207707176</v>
+        <v>1.099355282841521</v>
       </c>
     </row>
     <row r="93">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.9699376660659755</v>
+        <v>1.049843123237619</v>
       </c>
     </row>
     <row r="94">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.9436805597696323</v>
+        <v>1.075737717939543</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.9107227491939904</v>
+        <v>1.049803407601573</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.8657408108571926</v>
+        <v>1.058355507896792</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.9532980632474692</v>
+        <v>1.026291751062393</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.8921588659593281</v>
+        <v>1.116869878337768</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.001973419534642</v>
+        <v>1.078928207368574</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0.9467853346132548</v>
+        <v>1.039411149502893</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.080377966612559</v>
+        <v>1.033387611369263</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.9706729499930857</v>
+        <v>1.081787733163878</v>
       </c>
     </row>
     <row r="103">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.9701852697488386</v>
+        <v>1.039186094231966</v>
       </c>
     </row>
     <row r="104">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.046931474898769</v>
+        <v>1.032685968465785</v>
       </c>
     </row>
     <row r="105">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.9589717947065785</v>
+        <v>1.087718601480069</v>
       </c>
     </row>
     <row r="106">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.9821464790562153</v>
+        <v>0.9927320386035983</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.025620285277548</v>
+        <v>1.037372413519203</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.9750312213286814</v>
+        <v>0.9826707441386242</v>
       </c>
     </row>
     <row r="109">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.9398520295049628</v>
+        <v>1.020228497292733</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.8724541903749023</v>
+        <v>1.078107417556959</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.002641837330418</v>
+        <v>1.027125779419357</v>
       </c>
     </row>
     <row r="112">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.9567784813456368</v>
+        <v>1.011371910454479</v>
       </c>
     </row>
     <row r="113">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.9819252288081741</v>
+        <v>1.05234520830852</v>
       </c>
     </row>
     <row r="114">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.9237306376574632</v>
+        <v>1.068125554364087</v>
       </c>
     </row>
     <row r="115">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.023698975489298</v>
+        <v>1.048201543614396</v>
       </c>
     </row>
     <row r="116">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.9408084409645804</v>
+        <v>0.9830811390444418</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.9263253210548297</v>
+        <v>1.04027165495055</v>
       </c>
     </row>
     <row r="118">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.9932320735560173</v>
+        <v>1.072666375418666</v>
       </c>
     </row>
     <row r="119">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.9725716801153312</v>
+        <v>1.055085587195679</v>
       </c>
     </row>
     <row r="120">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.8446448438280272</v>
+        <v>1.023524895084563</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.9794315142973726</v>
+        <v>1.024200060897293</v>
       </c>
     </row>
     <row r="122">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.857067396367858</v>
+        <v>1.01010101010101</v>
       </c>
     </row>
     <row r="123">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.9838961352884978</v>
+        <v>0.9982657505593284</v>
       </c>
     </row>
     <row r="124">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.9510044791614783</v>
+        <v>1.033016932099501</v>
       </c>
     </row>
     <row r="125">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.943335739398774</v>
+        <v>1.027761229596092</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.9090010654652424</v>
+        <v>1.051511179951547</v>
       </c>
     </row>
     <row r="127">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.9524483355060929</v>
+        <v>0.9861524815653255</v>
       </c>
     </row>
     <row r="128">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.9138676531038586</v>
+        <v>1.03943762659358</v>
       </c>
     </row>
     <row r="129">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.9600276401033795</v>
+        <v>1.008949256655679</v>
       </c>
     </row>
     <row r="130">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.9913864886460421</v>
+        <v>1.042230959662149</v>
       </c>
     </row>
     <row r="131">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.9704132384841891</v>
+        <v>1.022810013635702</v>
       </c>
     </row>
     <row r="132">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.9854791026950492</v>
+        <v>1.049432728331811</v>
       </c>
     </row>
     <row r="133">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.9823070476873099</v>
+        <v>1.028899744496075</v>
       </c>
     </row>
     <row r="134">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.8725349060819583</v>
+        <v>1.016680567139283</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.8271696614200463</v>
+        <v>0.9990733018255954</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.046102922629194</v>
+        <v>1.040364324767995</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.9888698418098286</v>
+        <v>1.111852469650635</v>
       </c>
     </row>
     <row r="138">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.9187519177783535</v>
+        <v>1.032805115373906</v>
       </c>
     </row>
     <row r="139">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.011377896351071</v>
+        <v>1.005824959953404</v>
       </c>
     </row>
     <row r="140">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1.065984744484597</v>
+        <v>1.014959556243957</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.064918100537315</v>
+        <v>0.9968889418430749</v>
       </c>
     </row>
     <row r="142">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.9536906542833818</v>
+        <v>0.9682010140725738</v>
       </c>
     </row>
     <row r="143">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.9295658934514042</v>
+        <v>1.002793333068563</v>
       </c>
     </row>
     <row r="144">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.8970905288788802</v>
+        <v>0.9848551041211591</v>
       </c>
     </row>
     <row r="145">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.046848100549704</v>
+        <v>0.9002210837073222</v>
       </c>
     </row>
     <row r="146">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.9776404497146304</v>
+        <v>0.8900009266981743</v>
       </c>
     </row>
     <row r="147">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.9035489315030408</v>
+        <v>0.9060592822061373</v>
       </c>
     </row>
     <row r="148">
@@ -2353,194 +2353,194 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.985243984309605</v>
+        <v>0.4966705058448178</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.8994674278873835</v>
+        <v>0.4293127871109523</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.026127631717586</v>
+        <v>0.7371751591935078</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.027554050614124</v>
+        <v>0.8558984338800852</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.9464938177330576</v>
+        <v>0.8799661093239075</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.9348028909855869</v>
+        <v>0.9741054052980658</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>152</v>
+        <v>5</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.9778458519055928</v>
+        <v>1.045712697088844</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.038003647043087</v>
+        <v>1.007082621761521</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.148023317544584</v>
+        <v>1.025298860161246</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.091556436406414</v>
+        <v>1.026847769967036</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.8429263228278274</v>
+        <v>1.026874247057733</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.8371800828110566</v>
+        <v>0.9980539338337503</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.8151423465454635</v>
+        <v>1.013132636985848</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.8058710596570847</v>
+        <v>0.9964388313012166</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.010121014884165</v>
+        <v>1.001350331625561</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -2548,12 +2548,12 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.450513208734023</v>
+        <v>1.017660219495082</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -2561,12 +2561,12 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.9791657019793887</v>
+        <v>1.009121357745211</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -2574,12 +2574,12 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.9026055695079535</v>
+        <v>1.009902431920781</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -2587,12 +2587,12 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.8807828545409572</v>
+        <v>1.006870805035943</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -2600,12 +2600,12 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.9260564865068805</v>
+        <v>1.006526602856878</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -2613,12 +2613,12 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.9399286856262684</v>
+        <v>0.9864702066536929</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -2626,12 +2626,12 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.960882236540655</v>
+        <v>0.9752571587433988</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -2639,12 +2639,12 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1.037900302408168</v>
+        <v>0.9736023405748175</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -2652,12 +2652,12 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.9725154181610929</v>
+        <v>0.9832532401339741</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -2665,12 +2665,12 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0.9777482206161553</v>
+        <v>0.9760779485550179</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -2678,12 +2678,12 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.026226554272353</v>
+        <v>0.9604961806796647</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -2691,12 +2691,12 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1.012855926159622</v>
+        <v>0.9750453420178206</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -2704,12 +2704,12 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1.063213594568952</v>
+        <v>0.9969286574791161</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -2717,12 +2717,12 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.007671062637653</v>
+        <v>0.986390775381599</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -2730,12 +2730,12 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.031877037892832</v>
+        <v>1.007837218846393</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -2743,12 +2743,12 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1.061574158742787</v>
+        <v>0.987026225558337</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -2756,12 +2756,12 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.047939778060455</v>
+        <v>1.009346413016137</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -2769,12 +2769,12 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1.022140614378054</v>
+        <v>0.9538504309146507</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -2782,12 +2782,12 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.9942559913592049</v>
+        <v>0.9509114738472497</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1.017788809472951</v>
+        <v>0.9785800336259056</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -2808,12 +2808,12 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1.041157251279959</v>
+        <v>1.042297152388896</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -2821,12 +2821,12 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.041213203293146</v>
+        <v>0.9882176946397193</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -2834,12 +2834,12 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.055182607711231</v>
+        <v>1.012550140990514</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1.018042499032457</v>
+        <v>1.007360631213843</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -2860,12 +2860,12 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1.021785922497119</v>
+        <v>1.042178005480758</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -2873,12 +2873,12 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1.029595189913894</v>
+        <v>1.06537193693157</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -2886,12 +2886,12 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.9769945167135273</v>
+        <v>1.077101288110462</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -2899,12 +2899,12 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1.034483592474875</v>
+        <v>1.005652858863863</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -2912,12 +2912,12 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0.985941009376274</v>
+        <v>1.011808782450984</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -2925,12 +2925,12 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1.198099399817954</v>
+        <v>0.9990335861895495</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -2938,12 +2938,12 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1.109829777953338</v>
+        <v>1.070760024888465</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -2951,12 +2951,12 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.9557467749292216</v>
+        <v>1.011967644995162</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -2964,12 +2964,12 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.9999777477185293</v>
+        <v>1.018481009306697</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -2977,12 +2977,12 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1.053093531393041</v>
+        <v>1.017289540225319</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -2990,12 +2990,12 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.9923925045270761</v>
+        <v>0.9967300792988866</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -3003,12 +3003,12 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1.032319249778797</v>
+        <v>1.012973774441661</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1.024034029088404</v>
+        <v>1.02622555833565</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -3029,12 +3029,12 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1.055489191915846</v>
+        <v>1.022042178005479</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1.06178519773431</v>
+        <v>0.9953929862186742</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -3055,12 +3055,12 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1.044520695895738</v>
+        <v>0.9201318559116723</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -3068,12 +3068,12 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.05421017125632</v>
+        <v>0.9771237936375552</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -3081,12 +3081,12 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1.026797467159885</v>
+        <v>0.9895415491745767</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -3094,12 +3094,12 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1.027588697936507</v>
+        <v>0.9867349775606656</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -3107,12 +3107,12 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1.07611236377091</v>
+        <v>1.046546725445808</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1.040639472030051</v>
+        <v>1.03496299826575</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -3133,12 +3133,12 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1.153855832575771</v>
+        <v>0.9794670161642639</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -3146,12 +3146,12 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.113998506412628</v>
+        <v>1.004408435601096</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -3159,12 +3159,12 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1.198821407278922</v>
+        <v>1.018176522763679</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -3172,12 +3172,12 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1.112222745533334</v>
+        <v>1.010987992639369</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -3185,12 +3185,12 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.09305308536752</v>
+        <v>1.005957345406887</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -3198,12 +3198,12 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.9847091143552839</v>
+        <v>0.9272939089452852</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1.060170715521343</v>
+        <v>1.035108622264586</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -3224,12 +3224,12 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1.018889551014277</v>
+        <v>1.01399314243351</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1.091745780667403</v>
+        <v>1.010471689370772</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -3250,12 +3250,12 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1.101071499311769</v>
+        <v>0.9423593735520341</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -3263,12 +3263,12 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1.067688140337611</v>
+        <v>1.010405496644029</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -3276,12 +3276,12 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1.093340806668525</v>
+        <v>1.006539841402224</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -3289,12 +3289,12 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1.026729327267685</v>
+        <v>0.9727815507632021</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -3302,12 +3302,12 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1.067999553931428</v>
+        <v>0.9828560837735149</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1.058826021228815</v>
+        <v>0.9757999391026915</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -3328,12 +3328,12 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.061909055495157</v>
+        <v>0.9677244264400228</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -3341,12 +3341,12 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1.13300549502223</v>
+        <v>1.015886254418364</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -3354,12 +3354,12 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1.06489323625979</v>
+        <v>1.004752637780161</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -3367,12 +3367,12 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.041852899842589</v>
+        <v>1.005110078504574</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -3380,12 +3380,12 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1.058301841976442</v>
+        <v>0.9951944080384447</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -3393,12 +3393,12 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.987304708543004</v>
+        <v>0.9651958642784332</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -3406,12 +3406,12 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1.077285711472815</v>
+        <v>1.014827170790474</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -3419,12 +3419,12 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1.082253237839753</v>
+        <v>1.037518037518038</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -3432,12 +3432,12 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1.113722962545628</v>
+        <v>1.02846287249957</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1.045092365656233</v>
+        <v>0.9687437944318678</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -3458,12 +3458,12 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1.129094207981237</v>
+        <v>0.9867349775606656</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -3471,12 +3471,12 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1.057540630978369</v>
+        <v>1.024491308894979</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -3484,12 +3484,12 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1.07944186013992</v>
+        <v>0.9981201265604935</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1.132944220613235</v>
+        <v>1.013463600619564</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -3510,12 +3510,12 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1.096804523287575</v>
+        <v>1.043673961105154</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -3523,12 +3523,12 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1.01198816277678</v>
+        <v>1.12505129936323</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -3536,12 +3536,12 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1.093072379275642</v>
+        <v>1.064379046030422</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -3549,12 +3549,12 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1.051236353476592</v>
+        <v>1.024319207805446</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -3562,12 +3562,12 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1.029025514275621</v>
+        <v>1.01525080424163</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -3575,12 +3575,12 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1.025120158470997</v>
+        <v>1.057336139904947</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1.093570109233855</v>
+        <v>1.052437878125952</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1.102660941483326</v>
+        <v>0.9874101433734461</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -3614,12 +3614,12 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1.102700029464929</v>
+        <v>1.027787706686789</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -3627,12 +3627,12 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1.015459578646605</v>
+        <v>0.9985040443755951</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -3640,12 +3640,12 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1.040610364221618</v>
+        <v>0.956696718164608</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -3653,12 +3653,12 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1.042375393968245</v>
+        <v>1.010431973734726</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -3666,12 +3666,12 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1.087340900766955</v>
+        <v>1.01670704422998</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -3679,12 +3679,12 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1.056846153085527</v>
+        <v>1.011239525000993</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -3692,12 +3692,12 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1.062997429729514</v>
+        <v>1.008538861749871</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -3705,12 +3705,12 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1.062392023779671</v>
+        <v>0.988323603002502</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1.044921011512142</v>
+        <v>1.007307677032452</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -3731,12 +3731,12 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1.036315795079419</v>
+        <v>0.9936454982326542</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -3744,12 +3744,12 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1.052792781283076</v>
+        <v>0.995181169493078</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -3757,12 +3757,12 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1.112454106622692</v>
+        <v>0.9808967790619167</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -3770,12 +3770,12 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1.072309658663956</v>
+        <v>0.9659239842726081</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1.14734261490895</v>
+        <v>1.01563472205674</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -3796,12 +3796,12 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1.035721518928656</v>
+        <v>1.002303506890663</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -3809,12 +3809,12 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1.084550662490017</v>
+        <v>0.9911963673431394</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1.057278076715489</v>
+        <v>1.00427605014761</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1.054865591196196</v>
+        <v>1.023975005626382</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -3848,12 +3848,12 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1.041164665266583</v>
+        <v>0.9329467678091738</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -3861,12 +3861,12 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1.026509668107813</v>
+        <v>0.9850933979374347</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -3874,12 +3874,12 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1.082648159967724</v>
+        <v>0.9678965275295716</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -3887,12 +3887,12 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1.068894464192646</v>
+        <v>1.001773965076717</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -3900,12 +3900,12 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1.023575466258637</v>
+        <v>1.027681798324</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -3913,12 +3913,12 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1.041499008463979</v>
+        <v>1.049988747236454</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -3926,12 +3926,12 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1.082240647492294</v>
+        <v>0.9966109323907488</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -3939,12 +3939,12 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1.055822251384335</v>
+        <v>0.9905741557117704</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -3952,12 +3952,12 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1.06005652296108</v>
+        <v>0.9576631319750586</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -3965,12 +3965,12 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1.154674928510565</v>
+        <v>1.043382713107458</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -3978,12 +3978,12 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1.074671954100842</v>
+        <v>1.02572249361239</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -3991,12 +3991,12 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1.080271887870981</v>
+        <v>0.9391026913962693</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -4004,12 +4004,12 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1.053202852807595</v>
+        <v>0.9479989938705535</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1.021321797991442</v>
+        <v>0.9621377603028979</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -4030,12 +4030,12 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1.091512720000491</v>
+        <v>1.005401326502232</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -4043,12 +4043,12 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1.037120069753152</v>
+        <v>1.004620252326674</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -4056,12 +4056,12 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>1.069139045196908</v>
+        <v>1.005533711955726</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -4069,12 +4069,12 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>1.093295408069811</v>
+        <v>1.001204707626726</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -4082,12 +4082,12 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>1.060332090711126</v>
+        <v>0.9692203820644109</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -4095,12 +4095,12 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>1.111402975133124</v>
+        <v>0.9547638905437071</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -4108,12 +4108,12 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>1.104410368875334</v>
+        <v>1.017713173676484</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -4121,12 +4121,12 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>1.104501206592519</v>
+        <v>1.039900975680792</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -4134,12 +4134,12 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>1.070243727489023</v>
+        <v>0.9798509339793683</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>1.058958551167515</v>
+        <v>0.9641103035598746</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1.051609327669836</v>
+        <v>0.9860465732025354</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -4173,12 +4173,12 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1.101475807205839</v>
+        <v>1.01421819770444</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -4186,12 +4186,12 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>1.015630589331952</v>
+        <v>1.001946066166262</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -4199,12 +4199,12 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>1.080877927172174</v>
+        <v>1.020440314018326</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -4212,12 +4212,12 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1.101955320868832</v>
+        <v>0.9867879317420601</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -4225,12 +4225,12 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>1.021298847773736</v>
+        <v>0.9851331135734805</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -4238,12 +4238,12 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1.041810858113091</v>
+        <v>0.8360141387664421</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -4251,12 +4251,12 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>1.056500607451436</v>
+        <v>0.8293419119107363</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -4264,12 +4264,12 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>1.074020856503313</v>
+        <v>0.6870143108675525</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -4277,384 +4277,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1.090166822201671</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>134</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>1.26263942739899</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>135</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>1.051610141004079</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>136</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>1.113439627999029</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>137</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>1.105482610443455</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>138</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>1.065422407106134</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>139</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>1.04555789110451</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>140</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>1.058212306997576</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>141</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>1.106626997651513</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>142</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>1.029649026812691</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>143</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>1.17060691279038</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>144</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>1.00742854385409</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>145</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>1.004254033436499</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>146</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>1.09841783853348</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>147</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>1.029880273863693</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>148</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>1.10409021495359</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>149</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>1.145853810334699</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>150</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>0.9828377096674826</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>151</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>0.9886488524285995</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>152</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>1.066588787077969</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>153</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>1.031348151513928</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>154</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>1.00902403775099</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>155</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>0.9932013150097011</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>156</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>0.9850041035038017</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>157</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>1.015093841381518</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>158</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>0.939957819642592</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>159</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>0.9163982243729861</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>160</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>0.8363416615387128</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>161</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>0.8394317545197593</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>162</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>1.163319320062435</v>
+        <v>0.4583449170605134</v>
       </c>
     </row>
   </sheetData>
